--- a/backend/excel-templates/New-Test-data/bachelor_supervisor_users_test_data.xlsx
+++ b/backend/excel-templates/New-Test-data/bachelor_supervisor_users_test_data.xlsx
@@ -418,36 +418,36 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>dr..dineshkoirala@pcampus.edu.np</v>
+        <v>dinesh.koirala@pcampus.edu.np</v>
       </c>
       <c r="B2" t="str">
         <v>Test@123</v>
       </c>
       <c r="C2" t="str">
-        <v>Dr.</v>
+        <v>Dinesh</v>
       </c>
       <c r="D2" t="str">
-        <v>Dinesh Koirala</v>
+        <v>Koirala</v>
       </c>
       <c r="E2" t="str">
-        <v>Prof.</v>
+        <v>Prof. Dr.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>prof..dr.meenashrestha@pcampus.edu.np</v>
+        <v>meena.shrestha@pcampus.edu.np</v>
       </c>
       <c r="B3" t="str">
         <v>Test@123</v>
       </c>
       <c r="C3" t="str">
-        <v>Prof.</v>
+        <v>Meena</v>
       </c>
       <c r="D3" t="str">
-        <v>Dr. Meena Shrestha</v>
+        <v>Shrestha</v>
       </c>
       <c r="E3" t="str">
-        <v>Assoc.</v>
+        <v>Assoc. Prof. Dr.</v>
       </c>
     </row>
     <row r="4">
@@ -469,19 +469,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>prof..dr.gyanendrathapa@pcampus.edu.np</v>
+        <v>gyanendra.thapa@pcampus.edu.np</v>
       </c>
       <c r="B5" t="str">
         <v>Test@123</v>
       </c>
       <c r="C5" t="str">
-        <v>Prof.</v>
+        <v>Gyanendra</v>
       </c>
       <c r="D5" t="str">
-        <v>Dr. Gyanendra Thapa</v>
+        <v>Thapa</v>
       </c>
       <c r="E5" t="str">
-        <v>Assoc.</v>
+        <v>Assoc. Prof. Dr.</v>
       </c>
     </row>
     <row r="6">
@@ -503,19 +503,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>dr..rajupoudel@pcampus.edu.np</v>
+        <v>raju.poudel@pcampus.edu.np</v>
       </c>
       <c r="B7" t="str">
         <v>Test@123</v>
       </c>
       <c r="C7" t="str">
-        <v>Dr.</v>
+        <v>Raju</v>
       </c>
       <c r="D7" t="str">
-        <v>Raju Poudel</v>
+        <v>Poudel</v>
       </c>
       <c r="E7" t="str">
-        <v>Prof.</v>
+        <v>Prof. Dr.</v>
       </c>
     </row>
   </sheetData>
